--- a/StructureDefinition-SEEHDSDevice.xlsx
+++ b/StructureDefinition-SEEHDSDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSDevice.xlsx
+++ b/StructureDefinition-SEEHDSDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSDevice.xlsx
+++ b/StructureDefinition-SEEHDSDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSDevice.xlsx
+++ b/StructureDefinition-SEEHDSDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,7 +91,7 @@
 deviceName[systemName]  = sourceSystemName     (1..1, obligatorisk)
 deviceName[productName] = sourceSystemProductName (0..1)
 version                 = sourceSystemProductVersion (0..1)
-extension[sourceSystemContact] = sourceSystemContact.actorId/actorName (0..1)</t>
+extension[sourceSystemContact] = sourceSystemContact.hsaid/personName (0..1)</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -460,7 +460,7 @@
     <t>Kontaktperson för källsystemet (registrationRecord.sourceSystemContact)</t>
   </si>
   <si>
-    <t>Ansvarig kontaktperson för källsystemet (registrationRecord.sourceSystemContact.actorId/actorName).</t>
+    <t>Ansvarig kontaktperson för källsystemet (registrationRecord.sourceSystemContact.hsaid/personName).</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1

--- a/StructureDefinition-SEEHDSDevice.xlsx
+++ b/StructureDefinition-SEEHDSDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSDevice.xlsx
+++ b/StructureDefinition-SEEHDSDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSDevice.xlsx
+++ b/StructureDefinition-SEEHDSDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSDevice.xlsx
+++ b/StructureDefinition-SEEHDSDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSDevice.xlsx
+++ b/StructureDefinition-SEEHDSDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
